--- a/deliverables/Календарный план - pulse!.xlsx
+++ b/deliverables/Календарный план - pulse!.xlsx
@@ -261,7 +261,7 @@
     <t>3.2</t>
   </si>
   <si>
-    <t>Построить baseline профиля навыков</t>
+    <t>Построить начальную оценку навыков</t>
   </si>
   <si>
     <t>12.11.2026</t>
@@ -294,7 +294,7 @@
     <t>3.4</t>
   </si>
   <si>
-    <t>Обучить и проверить модель pass</t>
+    <t>Обучить и проверить прогноз прохождения</t>
   </si>
   <si>
     <t>T13</t>
@@ -303,7 +303,7 @@
     <t>3.5</t>
   </si>
   <si>
-    <t>Обучить и проверить модель accuracy</t>
+    <t>Обучить и проверить прогноз точности</t>
   </si>
   <si>
     <t>23.11.2026</t>
@@ -336,7 +336,7 @@
     <t>4.2</t>
   </si>
   <si>
-    <t>Связать оценки, модели и fallback</t>
+    <t>Связать оценки и модели с приложением</t>
   </si>
   <si>
     <t>27.11.2026</t>
@@ -486,7 +486,7 @@
     <t>Официальная дата сдачи</t>
   </si>
   <si>
-    <t>TBD; после объявления пересчитать обратным планированием.</t>
+    <t>Пока не объявлена; после объявления пересчитать план.</t>
   </si>
   <si>
     <t>Календарь</t>
@@ -504,7 +504,7 @@
     <t>Ресурсы</t>
   </si>
   <si>
-    <t>Роли назначены предварительно. Перегрузку ML и совмещение ролей нужно проверить в ProjectLibre.</t>
+    <t>Проверить, не назначено ли одному участнику несколько одновременных задач.</t>
   </si>
   <si>
     <t>Связи</t>

--- a/deliverables/Календарный план - pulse!.xlsx
+++ b/deliverables/Календарный план - pulse!.xlsx
@@ -12,22 +12,22 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">План!$A$5:$J$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">План!$A$1:$T$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">План!$A$1:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="152">
   <si>
     <t>Календарный план - pulse!</t>
   </si>
   <si>
-    <t>Черновик: старт 19.10.2026, дата сдачи не объявлена. Расчет по понедельникам-пятницам, без государственных праздников и выравнивания ресурсов.</t>
-  </si>
-  <si>
-    <t>20 работ, 5 вех, расчетная длительность 46 рабочих дней; окончание 21.12.2026; резерв 3 рабочих дня до 24.12.2026.</t>
+    <t>Старт 19.10.2026, сдача 14.11.2026. Рабочие дни: понедельник-пятница, кроме 4 ноября. Дорабатываем существующий прототип.</t>
+  </si>
+  <si>
+    <t>20 работ, 5 вех, 17 рабочих дней; окончание 11.11.2026; резерв 2 рабочих дня до 13.11.2026.</t>
   </si>
   <si>
     <t>ID</t>
@@ -72,24 +72,6 @@
     <t>09.11</t>
   </si>
   <si>
-    <t>16.11</t>
-  </si>
-  <si>
-    <t>23.11</t>
-  </si>
-  <si>
-    <t>30.11</t>
-  </si>
-  <si>
-    <t>07.12</t>
-  </si>
-  <si>
-    <t>14.12</t>
-  </si>
-  <si>
-    <t>21.12</t>
-  </si>
-  <si>
     <t>T01</t>
   </si>
   <si>
@@ -105,351 +87,303 @@
     <t>19.10.2026</t>
   </si>
   <si>
+    <t>Заказчик / руководитель</t>
+  </si>
+  <si>
+    <t>T02</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Уточнить требования и приемку</t>
+  </si>
+  <si>
     <t>20.10.2026</t>
   </si>
   <si>
-    <t>PM / Ляхов Я.П.</t>
-  </si>
-  <si>
-    <t>T02</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Уточнить требования и приемку</t>
+    <t>T03</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Проверить ТЗ, WBS и план</t>
   </si>
   <si>
     <t>21.10.2026</t>
   </si>
   <si>
+    <t>M01</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Веха: ТЗ и WBS согласованы</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>T04</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Данные</t>
+  </si>
+  <si>
+    <t>Добавить хранение сырых попыток</t>
+  </si>
+  <si>
+    <t>22.10.2026</t>
+  </si>
+  <si>
+    <t>Разработка</t>
+  </si>
+  <si>
+    <t>T05</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Проверить импорт профиля и карт</t>
+  </si>
+  <si>
+    <t>Тесты и документы</t>
+  </si>
+  <si>
+    <t>T06</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Подготовить сбор данных добровольцев</t>
+  </si>
+  <si>
+    <t>T07</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Собрать пилотные попытки</t>
+  </si>
+  <si>
     <t>23.10.2026</t>
   </si>
   <si>
-    <t>T03</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Проверить ТЗ, WBS и план</t>
-  </si>
-  <si>
     <t>26.10.2026</t>
   </si>
   <si>
+    <t>T04, T05, T06</t>
+  </si>
+  <si>
+    <t>T08</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Очистить данные и проверить утечки</t>
+  </si>
+  <si>
     <t>27.10.2026</t>
   </si>
   <si>
-    <t>M01</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>Веха: ТЗ и WBS согласованы</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>T04</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>Данные</t>
-  </si>
-  <si>
-    <t>Добавить хранение сырых попыток</t>
+    <t>Данные и модели</t>
+  </si>
+  <si>
+    <t>M02</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>Веха: данные готовы</t>
+  </si>
+  <si>
+    <t>T09</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Признаки и модели</t>
+  </si>
+  <si>
+    <t>Определить скиллсеты и признаки</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Построить начальную оценку навыков</t>
   </si>
   <si>
     <t>28.10.2026</t>
   </si>
   <si>
+    <t>M02, T09</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Рассчитать сложность карты по навыкам</t>
+  </si>
+  <si>
+    <t>29.10.2026</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Обучить и проверить прогноз прохождения</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Обучить и проверить прогноз точности</t>
+  </si>
+  <si>
     <t>30.10.2026</t>
   </si>
   <si>
-    <t>DEV / Гайфуллин А.Р.</t>
-  </si>
-  <si>
-    <t>T05</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>Проверить импорт профиля и карт</t>
-  </si>
-  <si>
-    <t>29.10.2026</t>
-  </si>
-  <si>
-    <t>QA / Темиров А.М.</t>
-  </si>
-  <si>
-    <t>T06</t>
-  </si>
-  <si>
-    <t>2.3</t>
-  </si>
-  <si>
-    <t>Подготовить сбор данных добровольцев</t>
-  </si>
-  <si>
-    <t>T07</t>
-  </si>
-  <si>
-    <t>2.4</t>
-  </si>
-  <si>
-    <t>Собрать пилотные попытки</t>
-  </si>
-  <si>
     <t>02.11.2026</t>
   </si>
   <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Приложение</t>
+  </si>
+  <si>
+    <t>Обновить экран профиля и карты</t>
+  </si>
+  <si>
+    <t>T04, T05, T09</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Связать оценки и модели с приложением</t>
+  </si>
+  <si>
+    <t>03.11.2026</t>
+  </si>
+  <si>
+    <t>T11, T12, T13, T14</t>
+  </si>
+  <si>
+    <t>M03</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Веха: MVP готов к показу</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Проверка</t>
+  </si>
+  <si>
+    <t>Провести автоматические тесты</t>
+  </si>
+  <si>
+    <t>05.11.2026</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Провести пилот с игроками</t>
+  </si>
+  <si>
     <t>06.11.2026</t>
   </si>
   <si>
-    <t>T04, T05, T06</t>
-  </si>
-  <si>
-    <t>T08</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>Очистить данные и проверить утечки</t>
-  </si>
-  <si>
     <t>09.11.2026</t>
   </si>
   <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>Проверить прогноз на новых попытках</t>
+  </si>
+  <si>
+    <t>10.11.2026</t>
+  </si>
+  <si>
+    <t>M04</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>Веха: проверка завершена</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Передача</t>
+  </si>
+  <si>
+    <t>Обновить инструкцию и документы</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Исправить критичные дефекты и принять</t>
+  </si>
+  <si>
     <t>11.11.2026</t>
   </si>
   <si>
-    <t>ML / Недугов Д.</t>
-  </si>
-  <si>
-    <t>M02</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>Веха: данные готовы</t>
-  </si>
-  <si>
-    <t>T09</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Признаки и модели</t>
-  </si>
-  <si>
-    <t>Определить скиллсеты и признаки</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>Построить начальную оценку навыков</t>
-  </si>
-  <si>
-    <t>12.11.2026</t>
-  </si>
-  <si>
-    <t>17.11.2026</t>
-  </si>
-  <si>
-    <t>M02, T09</t>
-  </si>
-  <si>
-    <t>T11</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t>Рассчитать сложность карты по навыкам</t>
-  </si>
-  <si>
-    <t>18.11.2026</t>
-  </si>
-  <si>
-    <t>20.11.2026</t>
-  </si>
-  <si>
-    <t>T12</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>Обучить и проверить прогноз прохождения</t>
-  </si>
-  <si>
-    <t>T13</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>Обучить и проверить прогноз точности</t>
-  </si>
-  <si>
-    <t>23.11.2026</t>
-  </si>
-  <si>
-    <t>26.11.2026</t>
-  </si>
-  <si>
-    <t>T14</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>Приложение</t>
-  </si>
-  <si>
-    <t>Обновить экран профиля и карты</t>
-  </si>
-  <si>
-    <t>03.11.2026</t>
-  </si>
-  <si>
-    <t>T05, T09</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>Связать оценки и модели с приложением</t>
-  </si>
-  <si>
-    <t>27.11.2026</t>
-  </si>
-  <si>
-    <t>01.12.2026</t>
-  </si>
-  <si>
-    <t>T11, T12, T13, T14</t>
-  </si>
-  <si>
-    <t>M03</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>Веха: MVP готов к показу</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>Проверка</t>
-  </si>
-  <si>
-    <t>Провести автоматические тесты</t>
-  </si>
-  <si>
-    <t>02.12.2026</t>
-  </si>
-  <si>
-    <t>04.12.2026</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>Провести пилот с игроками</t>
-  </si>
-  <si>
-    <t>07.12.2026</t>
-  </si>
-  <si>
-    <t>09.12.2026</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>Проверить прогноз на новых попытках</t>
-  </si>
-  <si>
-    <t>10.12.2026</t>
-  </si>
-  <si>
-    <t>14.12.2026</t>
-  </si>
-  <si>
-    <t>M04</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>Веха: проверка завершена</t>
-  </si>
-  <si>
-    <t>T19</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>Передача</t>
-  </si>
-  <si>
-    <t>Обновить инструкцию и документы</t>
-  </si>
-  <si>
-    <t>15.12.2026</t>
-  </si>
-  <si>
-    <t>16.12.2026</t>
-  </si>
-  <si>
-    <t>T16, T18</t>
-  </si>
-  <si>
-    <t>T20</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>Исправить критичные дефекты и принять</t>
-  </si>
-  <si>
-    <t>17.12.2026</t>
-  </si>
-  <si>
-    <t>21.12.2026</t>
-  </si>
-  <si>
     <t>T19, M04</t>
   </si>
   <si>
@@ -480,19 +414,19 @@
     <t>Внутренний резерв</t>
   </si>
   <si>
-    <t>3 рабочих дня до 24.12.2026</t>
+    <t>2 рабочих дня до 13.11.2026</t>
   </si>
   <si>
     <t>Официальная дата сдачи</t>
   </si>
   <si>
-    <t>Пока не объявлена; после объявления пересчитать план.</t>
+    <t>14.11.2026</t>
   </si>
   <si>
     <t>Календарь</t>
   </si>
   <si>
-    <t>Понедельник-пятница. Государственные праздники и отпуска пока не учтены.</t>
+    <t>Понедельник-пятница. 4 ноября нерабочий день. Сдача 14 ноября в субботу, работы заканчиваем заранее.</t>
   </si>
   <si>
     <t>Критический путь</t>
@@ -528,19 +462,19 @@
     <t>Вехи</t>
   </si>
   <si>
-    <t>Веха: ТЗ и WBS согласованы - 27.10.2026</t>
-  </si>
-  <si>
-    <t>Веха: данные готовы - 11.11.2026</t>
-  </si>
-  <si>
-    <t>Веха: MVP готов к показу - 01.12.2026</t>
-  </si>
-  <si>
-    <t>Веха: проверка завершена - 14.12.2026</t>
-  </si>
-  <si>
-    <t>Веха: проект передан - 21.12.2026</t>
+    <t>Веха: ТЗ и WBS согласованы - 21.10.2026</t>
+  </si>
+  <si>
+    <t>Веха: данные готовы - 27.10.2026</t>
+  </si>
+  <si>
+    <t>Веха: MVP готов к показу - 03.11.2026</t>
+  </si>
+  <si>
+    <t>Веха: проверка завершена - 10.11.2026</t>
+  </si>
+  <si>
+    <t>Веха: проект передан - 11.11.2026</t>
   </si>
 </sst>
 </file>
@@ -967,7 +901,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="8.7109375" customWidth="1"/>
@@ -976,10 +910,10 @@
     <col min="5" max="8" width="15.7109375" customWidth="1"/>
     <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="20" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -993,7 +927,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1007,7 +941,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1021,7 +955,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,50 +998,32 @@
       <c r="N5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:14" ht="30" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="30" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -1116,40 +1032,34 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="7" spans="1:14" ht="30" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E7" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -1158,802 +1068,688 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-    </row>
-    <row r="8" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="8" spans="1:14" ht="30" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-    </row>
-    <row r="9" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="9" spans="1:14" ht="30" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="K9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-    </row>
-    <row r="10" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="10" spans="1:14" ht="30" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E10" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="J10" s="4">
         <v>0</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-    </row>
-    <row r="11" spans="1:20" ht="30" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="6">
+    </row>
+    <row r="11" spans="1:14" ht="30" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="9"/>
+      <c r="F11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-    </row>
-    <row r="12" spans="1:20" ht="30" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="6" t="s">
+    </row>
+    <row r="12" spans="1:14" ht="30" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="9"/>
+      <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-    </row>
-    <row r="13" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="13" spans="1:14" ht="30" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="30" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="4">
-        <v>5</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="30" customHeight="1">
+      <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-    </row>
-    <row r="14" spans="1:20" ht="30" customHeight="1">
-      <c r="A14" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="6">
+        <v>2</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="30" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="4">
-        <v>3</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-    </row>
-    <row r="15" spans="1:20" ht="30" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="I17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="30" customHeight="1">
+      <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="C18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="7">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-    </row>
-    <row r="16" spans="1:20" ht="30" customHeight="1">
-      <c r="A16" s="6" t="s">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="6">
-        <v>7</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-    </row>
-    <row r="17" spans="1:20" ht="30" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="4">
-        <v>4</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-    </row>
-    <row r="18" spans="1:20" ht="30" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J18" s="4">
         <v>0</v>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="L18" s="5"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-    </row>
-    <row r="19" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="19" spans="1:14" ht="30" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="6">
+        <v>2</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="30" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="30" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="6">
+        <v>4</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" ht="30" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="6">
-        <v>4</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" s="6">
-        <v>7</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-    </row>
-    <row r="20" spans="1:20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="G22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="4">
-        <v>4</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="4">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-    </row>
-    <row r="21" spans="1:20" ht="30" customHeight="1">
-      <c r="A21" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="6">
-        <v>4</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="6">
-        <v>14</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="6"/>
-    </row>
-    <row r="22" spans="1:20" ht="30" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="4">
-        <v>3</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J22" s="4">
         <v>0</v>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="M22" s="5"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-    </row>
-    <row r="23" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="23" spans="1:14" ht="30" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E23" s="7">
         <v>0</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J23" s="7">
         <v>0</v>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="M23" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-    </row>
-    <row r="24" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="24" spans="1:14" ht="30" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E24" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J24" s="4">
         <v>0</v>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="M24" s="5"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-    </row>
-    <row r="25" spans="1:20" ht="30" customHeight="1">
+    </row>
+    <row r="25" spans="1:14" ht="30" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E25" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J25" s="4">
         <v>0</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-    </row>
-    <row r="26" spans="1:20" ht="30" customHeight="1">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" ht="30" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E26" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J26" s="4">
         <v>0</v>
@@ -1961,85 +1757,73 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="6"/>
-    </row>
-    <row r="27" spans="1:20" ht="30" customHeight="1">
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" ht="30" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E27" s="7">
         <v>0</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J27" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="T27" s="6"/>
-    </row>
-    <row r="28" spans="1:20" ht="30" customHeight="1">
+      <c r="N27" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="30" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J28" s="4">
         <v>0</v>
@@ -2047,41 +1831,35 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="6"/>
-    </row>
-    <row r="29" spans="1:20" ht="30" customHeight="1">
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" ht="30" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E29" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4">
         <v>0</v>
@@ -2089,41 +1867,35 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="1:20" ht="30" customHeight="1">
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" ht="30" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="E30" s="7">
         <v>0</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J30" s="7">
         <v>0</v>
@@ -2131,14 +1903,8 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="8" t="s">
-        <v>43</v>
+      <c r="N30" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2164,140 +1930,140 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="35" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="35" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="35" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="35" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="35" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="35" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="35" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="35" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="35" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="35" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="35" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="6" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="6" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="6" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
